--- a/artfynd/A 67738-2021 artfynd.xlsx
+++ b/artfynd/A 67738-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116992937</v>
+        <v>116992930</v>
       </c>
       <c r="B2" t="n">
-        <v>90452</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495454</v>
+        <v>495444</v>
       </c>
       <c r="R2" t="n">
-        <v>7073519</v>
+        <v>7073536</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>klen granlåga utan matkkontakt, till stor del kvarsittande bark, men börjar falla av.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116992926</v>
+        <v>116992937</v>
       </c>
       <c r="B3" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495508</v>
+        <v>495454</v>
       </c>
       <c r="R3" t="n">
-        <v>7073477</v>
+        <v>7073519</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,11 +854,6 @@
           <t>2023-10-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -885,6 +875,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>116992926</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kojflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>495508</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7073477</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
